--- a/prompt_library_all_prompts_with_guide.xlsx
+++ b/prompt_library_all_prompts_with_guide.xlsx
@@ -5,27 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37F17BE-9236-4E55-B2F5-79EE12DD426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB47679-29E4-4514-B9E4-CA2D9E74C664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User Guide" sheetId="1" r:id="rId1"/>
     <sheet name="Prompt_Library" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Prompt_Library!$A$1:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Prompt_Library!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="230">
   <si>
     <t>Prompt Library – User Guide</t>
   </si>
@@ -742,21 +741,9 @@
     <t>Prompt ID</t>
   </si>
   <si>
-    <t>feedback/Review</t>
-  </si>
-  <si>
-    <t>prompt Update date</t>
-  </si>
-  <si>
     <t>6. Feedback</t>
   </si>
   <si>
-    <t>step 1: upload file</t>
-  </si>
-  <si>
-    <t>step 2: user guide from copilot to users, examples</t>
-  </si>
-  <si>
     <t>Public research</t>
   </si>
   <si>
@@ -764,6 +751,78 @@
   </si>
   <si>
     <t>write your feedback in the sheet below</t>
+  </si>
+  <si>
+    <t>AN-001</t>
+  </si>
+  <si>
+    <t>AN-002</t>
+  </si>
+  <si>
+    <t>CO-001</t>
+  </si>
+  <si>
+    <t>CO-002</t>
+  </si>
+  <si>
+    <t>CO-003</t>
+  </si>
+  <si>
+    <t>CO-004</t>
+  </si>
+  <si>
+    <t>CO-005</t>
+  </si>
+  <si>
+    <t>CO-006</t>
+  </si>
+  <si>
+    <t>CO-007</t>
+  </si>
+  <si>
+    <t>PU-001</t>
+  </si>
+  <si>
+    <t>PU-002</t>
+  </si>
+  <si>
+    <t>PU-003</t>
+  </si>
+  <si>
+    <t>PU-004</t>
+  </si>
+  <si>
+    <t>PU-005</t>
+  </si>
+  <si>
+    <t>PU-006</t>
+  </si>
+  <si>
+    <t>MA-001</t>
+  </si>
+  <si>
+    <t>MA-002</t>
+  </si>
+  <si>
+    <t>MA-003</t>
+  </si>
+  <si>
+    <t>MA-004</t>
+  </si>
+  <si>
+    <t>MA-005</t>
+  </si>
+  <si>
+    <t>MA-006</t>
+  </si>
+  <si>
+    <t>MA-007</t>
+  </si>
+  <si>
+    <t>MA-008</t>
+  </si>
+  <si>
+    <t>MA-009</t>
   </si>
 </sst>
 </file>
@@ -822,10 +881,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1128,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:B44"/>
+  <dimension ref="B1:B40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="110" customWidth="1"/>
@@ -1296,22 +1357,12 @@
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B43" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B44" t="s">
-        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1321,839 +1372,893 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="23.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>35</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>36</v>
-      </c>
-      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>38</v>
-      </c>
-      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>70</v>
-      </c>
-      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>67</v>
-      </c>
-      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>68</v>
-      </c>
-      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>69</v>
-      </c>
-      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>1</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>207</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>2</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>207</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>216</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>207</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>217</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>207</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>207</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>219</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>207</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>39</v>
-      </c>
-      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>72</v>
-      </c>
-      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>41</v>
-      </c>
-      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>74</v>
-      </c>
-      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>42</v>
-      </c>
-      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>73</v>
-      </c>
-      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>40</v>
-      </c>
-      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>9</v>
-      </c>
-      <c r="B24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M24" s="1"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>71</v>
-      </c>
-      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B711E28-511F-49C7-A66D-1B45BAD126E4}">
-  <dimension ref="B2:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/prompt_library_all_prompts_with_guide.xlsx
+++ b/prompt_library_all_prompts_with_guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB47679-29E4-4514-B9E4-CA2D9E74C664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86014378-4B88-41B5-BE1C-87894310ABE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="317">
   <si>
     <t>Prompt Library – User Guide</t>
   </si>
@@ -823,6 +823,267 @@
   </si>
   <si>
     <t>MA-009</t>
+  </si>
+  <si>
+    <t>ME-20251212-001</t>
+  </si>
+  <si>
+    <t>Meetings</t>
+  </si>
+  <si>
+    <t>Meeting Summary &amp; Action Items</t>
+  </si>
+  <si>
+    <t>meeting notes, minutes, decisions, action items, owners, due dates</t>
+  </si>
+  <si>
+    <t>Summarize a meeting clearly and extract decisions + action items with owners and due dates.</t>
+  </si>
+  <si>
+    <t>Meeting minutes assistant</t>
+  </si>
+  <si>
+    <t>Summarise the meeting in concise bullet points to capture the key discussions, decisions, and action items. Create a table listing all the actions, assign an owner to each, and set a due date. Ensure the summary is clear and professional for sharing with all attendees and relevant stakeholders.</t>
+  </si>
+  <si>
+    <t>Meeting transcript/notes; attendee list (optional); any known owners/dates (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulleted summary + Action table (Action </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Owner </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Due date </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Notes)</t>
+  </si>
+  <si>
+    <t>PR-20251212-002</t>
+  </si>
+  <si>
+    <t>Presentations</t>
+  </si>
+  <si>
+    <t>Slide Deck Outline Creation</t>
+  </si>
+  <si>
+    <t>slide deck, document summary, key takeaways, conclusion</t>
+  </si>
+  <si>
+    <t>Create a concise 10-slide deck outline based on a provided document.</t>
+  </si>
+  <si>
+    <t>Presentation strategist / slide designer</t>
+  </si>
+  <si>
+    <t>Please create a 10 page slide deck referencing [/document]. Include a slide on key takeaways and a conclusion. Keep it concise and self explanatory as much as possible.</t>
+  </si>
+  <si>
+    <t>Source document/link/text; target audience (optional); tone (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide-by-slide outline/table (Slide # </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Title </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Key bullets </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Speaker notes (optional))</t>
+  </si>
+  <si>
+    <t>EM-20251212-003</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Email Prioritization (Last 2 Weeks)</t>
+  </si>
+  <si>
+    <t>inbox triage, deadlines, follow-up, recap, VIP senders</t>
+  </si>
+  <si>
+    <t>List the most critical emails from the last two weeks, prioritized by deadlines, and separately list emails from specified people.</t>
+  </si>
+  <si>
+    <t>Email triage assistant</t>
+  </si>
+  <si>
+    <t>Please compile a list of the most critical emails I've received from the past two weeks, prioritising them by their deadlines. Additionally, look for emails from [/person] and [/person], these emails should be in a separate list. Don't focus on Teams messages, only emails and look for words like 'Follow up', 'Action' and 'Recap'.</t>
+  </si>
+  <si>
+    <t>Email inbox access; time window (last 2 weeks); VIP people list; definition of “critical” (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioritized email list + Separate VIP list (each item: Subject </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> From </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Date </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deadline (if any) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Why important </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Suggested action)</t>
+  </si>
+  <si>
+    <t>PR-20251212-004</t>
+  </si>
+  <si>
+    <t>Prompting</t>
+  </si>
+  <si>
+    <t>Prompt Refinement Workflow</t>
+  </si>
+  <si>
+    <t>prompt engineering, iterative improvement, clarifying questions, copilot</t>
+  </si>
+  <si>
+    <t>Iteratively improve a user’s prompt by asking clarifying questions and producing a revised version each round.</t>
+  </si>
+  <si>
+    <t>Prompt engineer</t>
+  </si>
+  <si>
+    <t>Become my Prompt engineer. Your goal is to help me craft the best possible prompt for my needs. The prompt will be used by you, Copilot. You will follow the following process: 1) First ask what the prompt should be about. 2) Based on my input, generate (a) Revised prompt (clear, concise, easy to understand) and (b) Questions (ask what additional info is needed). 3) Continue iterating until I say we are done.</t>
+  </si>
+  <si>
+    <t>Initial user goal/use-case; constraints (tone, length, audience); inputs/tools available (optional)</t>
+  </si>
+  <si>
+    <t>Two sections each iteration: (1) Revised Prompt (2) Questions</t>
+  </si>
+  <si>
+    <t>PR-20251212-005</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
+  <si>
+    <t>Daily Planning Executive Briefing</t>
+  </si>
+  <si>
+    <t>daily plan, calendar, meetings, teams summary, email actions, prioritization</t>
+  </si>
+  <si>
+    <t>Create an executive briefing for “today”: meetings list, Teams summary, actionable emails summary, and top 3 priorities.</t>
+  </si>
+  <si>
+    <t>Personal assistant / chief of staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hey Copilot, I am trying to plan ahead for today. I'd like you to act as my personal assistant and provide me with an overview of what is on my plate today. Step 1: Pull a list of all my meetings for today. Step 2: Aggregate all meeting info into a table with columns Time </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Meeting Title. Step 3: Summarise my Teams chats from today. Step 4: Go through my inbox and summarise any emails where I am in the to line and there is a direct action required; put into a table with columns Email Title </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Email Summary </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recommended Action. Step 5: Based on the above, suggest the top three actions I should focus on.</t>
+  </si>
+  <si>
+    <t>Issues of the day (date); calendar access; Teams chats/messages; email inbox access</t>
+  </si>
+  <si>
+    <t>Meeting table + Email action table + Top 3 action recommendations (bullets)</t>
+  </si>
+  <si>
+    <t>EM-20251212-006</t>
+  </si>
+  <si>
+    <t>Email Priority + Action Categorization</t>
+  </si>
+  <si>
+    <t>priority sorting, urgent, reply needed, cc, newsletters, promos, notifications</t>
+  </si>
+  <si>
+    <t>Categorize and prioritize emails (reply-first, frequent senders, urgent flags) and output top 10 emails before a specified cutoff.</t>
+  </si>
+  <si>
+    <t>Email triage analyst</t>
+  </si>
+  <si>
+    <t>Sort emails by priority: top priority = replies to messages I previously sent; group emails from the same person (higher priority for frequent senders); medium priority for regular emails from colleagues/clients/business-critical; low priority for emails where I'm CC (unless flagged urgent), newsletters, promotional emails, and automated notifications. Output 10 emails received before XXXX. Also categorize emails by action: "Immediate Action Needed" (replies/urgent keywords), "Pending Review" (non-urgent but needs attention), "For Reference" (newsletters/announcements/CC’d). Output 10 emails received before XXX.</t>
+  </si>
+  <si>
+    <t>Email inbox access; cutoff date/time (XXXX); definition of “urgent keywords” (optional); sent-mail access (for “replies to my messages”)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table of 10 emails (Subject </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Priority (High/Med/Low) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Action Category </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Why </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Next step)</t>
+  </si>
+  <si>
+    <t>PE-20251212-007</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Self-Review &amp; PDP Drafting</t>
+  </si>
+  <si>
+    <t>achievements, milestones, impact, objectives alignment, improvement areas, H1 2025</t>
+  </si>
+  <si>
+    <t>Synthesize work evidence from emails/meetings/docs into achievements + improvement areas aligned to objectives.</t>
+  </si>
+  <si>
+    <t>Career coach / performance review assistant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look at the emails, teams meetings, meeting transcripts, documents, teams chats that I've been involved in for the H1 2025. Use these messages to distil my achievements. Give me a breakdown like milestones, time taken in a table: Activity or Project Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Description </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> When started </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Major Achievements </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> How it helps me in my role </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> How it maps with organizations objectives. In another table give me a breakdown of 3 areas for improvement: Improvement area </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> description </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> how it impacts my role. Refer to my what and how objectives in these documents. PDP The What.</t>
+  </si>
+  <si>
+    <t>Artifacts for H1 2025 (emails, chats, docs, transcripts); role description (optional); org objectives; “what/how” objectives text</t>
+  </si>
+  <si>
+    <t>Achievements table + Improvement areas table (3 rows) + optional PDP “What” bullets</t>
   </si>
 </sst>
 </file>
@@ -1372,9 +1633,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="23.90625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.7265625" bestFit="1" customWidth="1"/>
@@ -1943,7 +2205,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1978,7 +2240,7 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2013,7 +2275,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2048,7 +2310,7 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2083,7 +2345,7 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2118,7 +2380,7 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2153,7 +2415,7 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2188,7 +2450,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2223,7 +2485,7 @@
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2257,6 +2519,292 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D26" t="s">
+        <v>232</v>
+      </c>
+      <c r="E26" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" t="s">
+        <v>234</v>
+      </c>
+      <c r="G26" t="s">
+        <v>235</v>
+      </c>
+      <c r="H26" t="s">
+        <v>236</v>
+      </c>
+      <c r="I26" t="s">
+        <v>237</v>
+      </c>
+      <c r="J26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" t="s">
+        <v>243</v>
+      </c>
+      <c r="D27" t="s">
+        <v>244</v>
+      </c>
+      <c r="E27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F27" t="s">
+        <v>246</v>
+      </c>
+      <c r="G27" t="s">
+        <v>247</v>
+      </c>
+      <c r="H27" t="s">
+        <v>248</v>
+      </c>
+      <c r="I27" t="s">
+        <v>249</v>
+      </c>
+      <c r="J27" t="s">
+        <v>250</v>
+      </c>
+      <c r="K27" t="s">
+        <v>239</v>
+      </c>
+      <c r="L27" t="s">
+        <v>240</v>
+      </c>
+      <c r="M27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" t="s">
+        <v>255</v>
+      </c>
+      <c r="D28" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" t="s">
+        <v>259</v>
+      </c>
+      <c r="H28" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28" t="s">
+        <v>261</v>
+      </c>
+      <c r="J28" t="s">
+        <v>262</v>
+      </c>
+      <c r="K28" t="s">
+        <v>251</v>
+      </c>
+      <c r="L28" t="s">
+        <v>252</v>
+      </c>
+      <c r="M28" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" t="s">
+        <v>269</v>
+      </c>
+      <c r="D29" t="s">
+        <v>270</v>
+      </c>
+      <c r="E29" t="s">
+        <v>271</v>
+      </c>
+      <c r="F29" t="s">
+        <v>272</v>
+      </c>
+      <c r="G29" t="s">
+        <v>273</v>
+      </c>
+      <c r="H29" t="s">
+        <v>274</v>
+      </c>
+      <c r="I29" t="s">
+        <v>275</v>
+      </c>
+      <c r="J29" t="s">
+        <v>276</v>
+      </c>
+      <c r="K29" t="s">
+        <v>263</v>
+      </c>
+      <c r="L29" t="s">
+        <v>264</v>
+      </c>
+      <c r="M29" t="s">
+        <v>265</v>
+      </c>
+      <c r="N29" t="s">
+        <v>266</v>
+      </c>
+      <c r="O29" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>277</v>
+      </c>
+      <c r="C30" t="s">
+        <v>278</v>
+      </c>
+      <c r="D30" t="s">
+        <v>279</v>
+      </c>
+      <c r="E30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F30" t="s">
+        <v>281</v>
+      </c>
+      <c r="G30" t="s">
+        <v>282</v>
+      </c>
+      <c r="H30" t="s">
+        <v>283</v>
+      </c>
+      <c r="I30" t="s">
+        <v>284</v>
+      </c>
+      <c r="J30" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C31" t="s">
+        <v>255</v>
+      </c>
+      <c r="D31" t="s">
+        <v>290</v>
+      </c>
+      <c r="E31" t="s">
+        <v>291</v>
+      </c>
+      <c r="F31" t="s">
+        <v>292</v>
+      </c>
+      <c r="G31" t="s">
+        <v>293</v>
+      </c>
+      <c r="H31" t="s">
+        <v>294</v>
+      </c>
+      <c r="I31" t="s">
+        <v>295</v>
+      </c>
+      <c r="J31" t="s">
+        <v>296</v>
+      </c>
+      <c r="K31" t="s">
+        <v>286</v>
+      </c>
+      <c r="L31" t="s">
+        <v>287</v>
+      </c>
+      <c r="M31" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>301</v>
+      </c>
+      <c r="C32" t="s">
+        <v>302</v>
+      </c>
+      <c r="D32" t="s">
+        <v>303</v>
+      </c>
+      <c r="E32" t="s">
+        <v>304</v>
+      </c>
+      <c r="F32" t="s">
+        <v>305</v>
+      </c>
+      <c r="G32" t="s">
+        <v>306</v>
+      </c>
+      <c r="H32" t="s">
+        <v>307</v>
+      </c>
+      <c r="I32" t="s">
+        <v>308</v>
+      </c>
+      <c r="J32" t="s">
+        <v>309</v>
+      </c>
+      <c r="K32" t="s">
+        <v>263</v>
+      </c>
+      <c r="L32" t="s">
+        <v>264</v>
+      </c>
+      <c r="M32" t="s">
+        <v>297</v>
+      </c>
+      <c r="N32" t="s">
+        <v>298</v>
+      </c>
+      <c r="O32" t="s">
+        <v>299</v>
+      </c>
+      <c r="P32" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" spans="11:17" x14ac:dyDescent="0.35">
+      <c r="K33" t="s">
+        <v>310</v>
+      </c>
+      <c r="L33" t="s">
+        <v>311</v>
+      </c>
+      <c r="M33" t="s">
+        <v>312</v>
+      </c>
+      <c r="N33" t="s">
+        <v>313</v>
+      </c>
+      <c r="O33" t="s">
+        <v>314</v>
+      </c>
+      <c r="P33" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>316</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
